--- a/data/governance_spec.xlsx
+++ b/data/governance_spec.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,7 +563,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D_rev</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>CEO</t>
         </is>
       </c>
     </row>
@@ -583,17 +583,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>D_rev</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>chance</t>
+          <t>decision</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>Board</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M_rev</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -623,17 +623,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>M_rev</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>decision</t>
+          <t>chance</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Nature</t>
         </is>
       </c>
     </row>
@@ -643,15 +643,55 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>D4_post_review</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D_rev_post_review</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>Terminal</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>terminal</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
@@ -668,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -976,6 +1016,138 @@
       <c r="D14" t="inlineStr">
         <is>
           <t>CEO negotiates managed exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>D4_post_review</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D4_stay</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>post_review_round</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CEO stays after adverse review findings</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>D4_post_review</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D4_resign</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>post_review_round</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CEO resigns after adverse review findings</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>D4_post_review</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D4_negotiate_exit</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>post_review_round</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CEO negotiates exit after adverse review findings</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>D_rev_post_review</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Drev_no_action</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>post_review_round</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Board takes no action after adverse review</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>D_rev_post_review</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Drev_sack_ceo</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>post_review_round_and_CEO_present</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Board sacks CEO after adverse review</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>D_rev_post_review</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Drev_commission_review</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>post_review_round_and_review_not_commissioned</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Board commissions review after adverse findings</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1088,7 +1260,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">
@@ -1139,6 +1311,66 @@
       </c>
       <c r="B10" t="n">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>second_strike_spill_penalty</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>board_regulatory_liability</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>board_d1_liability</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>qantas_legal_d1_penalty</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>qantas_legal_d_rev_penalty</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adverse_review_ceo_present_penalty</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1152,7 +1384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1204,7 +1436,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">
@@ -1235,6 +1467,16 @@
       </c>
       <c r="B8" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>market_alignment_bonus</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1290,7 +1532,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -1300,7 +1542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1552,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -1326,31 +1568,91 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D_agm</t>
+          <t>D_resign_late</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D_disgrace</t>
+          <t>D_negotiate</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>D_agm</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>D_disgrace</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>D_adverse_review</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B12" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>D_stay</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>loss_aversion</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>W_ref</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>loss_aversion_D</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.25</v>
       </c>
     </row>
   </sheetData>
@@ -1364,7 +1666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1426,7 +1728,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4">
@@ -1487,6 +1789,66 @@
       </c>
       <c r="D6" t="n">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D4_post_review</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>resign_vote_threshold</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D_rev_post_review</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>review_vote_threshold</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D_rev_post_review</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>sack_vote_threshold</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -1552,7 +1914,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">

--- a/data/governance_spec.xlsx
+++ b/data/governance_spec.xlsx
@@ -1208,7 +1208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1371,6 +1371,36 @@
       </c>
       <c r="B16" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ceo_loss_shock_strike</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ceo_loss_shock_overwhelming</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ceo_loss_shock_adverse</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/governance_spec.xlsx
+++ b/data/governance_spec.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="node_order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action_sets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="vote_thresholds" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="utilities_board" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="utilities_asa" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="utilities_ceo" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="policy_parameters" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="board_overconfidence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="node_order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="action_sets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="vote_thresholds" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="utilities_board" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="utilities_asa" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="utilities_ceo" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="policy_parameters" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="board_overconfidence" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>0.3439</v>
       </c>
     </row>
     <row r="9">
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0.411</v>
       </c>
     </row>
     <row r="10">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5</v>
+        <v>0.8572</v>
       </c>
     </row>
     <row r="11">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>0.300267</v>
       </c>
     </row>
     <row r="12">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>0.187667</v>
       </c>
     </row>
     <row r="13">
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>0.8951</v>
       </c>
     </row>
     <row r="15">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0.07506699999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>0.5709</v>
       </c>
     </row>
     <row r="17">
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4</v>
+        <v>0.0024</v>
       </c>
     </row>
     <row r="18">
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5</v>
+        <v>0.1205</v>
       </c>
     </row>
     <row r="19">
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/governance_spec.xlsx
+++ b/data/governance_spec.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="node_order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="action_sets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="vote_thresholds" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="utilities_board" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="utilities_asa" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="utilities_ceo" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="policy_parameters" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="board_overconfidence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="node_order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action_sets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="vote_thresholds" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="utilities_board" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="utilities_asa" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="utilities_ceo" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="policy_parameters" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="board_overconfidence" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1208,7 +1208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1306,7 +1306,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>early_ceo_departure_cost</t>
+          <t>board_passivity_after_departure</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1366,7 +1366,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>adverse_review_ceo_present_penalty</t>
+          <t>negative_review_finding_penalty</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1376,30 +1376,40 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ceo_loss_shock_strike</t>
+          <t>balanced_review_finding_penalty</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0024</v>
+        <v>0.2854</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ceo_loss_shock_overwhelming</t>
+          <t>ceo_loss_shock_strike</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1205</v>
+        <v>0.0024</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>ceo_loss_shock_overwhelming</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.1205</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>ceo_loss_shock_adverse</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B20" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/governance_spec.xlsx
+++ b/data/governance_spec.xlsx
@@ -1424,7 +1424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1442,47 +1442,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>vote_reward_weight</t>
+          <t>strike_ba_shift</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ceo_removal_reward</t>
+          <t>strike_ol_shift</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>review_car_weight</t>
+          <t>overwhelming_ba_shift</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mobilisation_cost</t>
+          <t>overwhelming_ol_shift</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>reputational_gain_weight</t>
+          <t>ceo_removal_ba_shift</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1492,31 +1492,71 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>overwhelming_reward_weight</t>
+          <t>ceo_removal_fw_shift</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>early_ceo_departure_reward</t>
+          <t>negative_review_td_shift</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>market_alignment_bonus</t>
+          <t>negative_review_egr_shift</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>balanced_review_td_shift</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>market_alignment_ol_shift</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>market_alignment_pf_shift</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mobilisation_cost</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
